--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/ARKANSAS_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/ARKANSAS_2013.xlsx
@@ -1885,7 +1885,7 @@
         <v>6</v>
       </c>
       <c r="D85">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="86">
@@ -2371,7 +2371,7 @@
         <v>6</v>
       </c>
       <c r="D112">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="113">
@@ -2389,7 +2389,7 @@
         <v>6</v>
       </c>
       <c r="D113">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="114">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C120">
@@ -2533,7 +2533,7 @@
         <v>6</v>
       </c>
       <c r="D121">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="122">
@@ -3973,7 +3973,7 @@
         <v>6</v>
       </c>
       <c r="D201">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="202">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C203">
@@ -4027,7 +4027,7 @@
         <v>6</v>
       </c>
       <c r="D204">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="205">
@@ -4279,7 +4279,7 @@
         <v>6</v>
       </c>
       <c r="D218">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="219">
@@ -4297,7 +4297,7 @@
         <v>6</v>
       </c>
       <c r="D219">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="220">
@@ -4603,7 +4603,7 @@
         <v>6</v>
       </c>
       <c r="D236">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="237">
@@ -5017,7 +5017,7 @@
         <v>6</v>
       </c>
       <c r="D259">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="260">
@@ -5323,7 +5323,7 @@
         <v>6</v>
       </c>
       <c r="D276">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="277">
@@ -5413,7 +5413,7 @@
         <v>6</v>
       </c>
       <c r="D281">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="282">
@@ -5521,7 +5521,7 @@
         <v>6</v>
       </c>
       <c r="D287">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="288">
@@ -5539,7 +5539,7 @@
         <v>6</v>
       </c>
       <c r="D288">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="289">
@@ -6889,7 +6889,7 @@
         <v>6</v>
       </c>
       <c r="D363">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="364">
@@ -6943,7 +6943,7 @@
         <v>6</v>
       </c>
       <c r="D366">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="367">
@@ -7069,7 +7069,7 @@
         <v>6</v>
       </c>
       <c r="D373">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="374">
@@ -7231,7 +7231,7 @@
         <v>6</v>
       </c>
       <c r="D382">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="383">
@@ -7411,7 +7411,7 @@
         <v>6</v>
       </c>
       <c r="D392">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="393">
@@ -7897,7 +7897,7 @@
         <v>6</v>
       </c>
       <c r="D419">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="420">
@@ -8365,7 +8365,7 @@
         <v>6</v>
       </c>
       <c r="D445">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="446">
@@ -8995,7 +8995,7 @@
         <v>6</v>
       </c>
       <c r="D480">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="481">
@@ -9103,7 +9103,7 @@
         <v>6</v>
       </c>
       <c r="D486">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="487">
@@ -9247,7 +9247,7 @@
         <v>6</v>
       </c>
       <c r="D494">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="495">
@@ -9265,7 +9265,7 @@
         <v>6</v>
       </c>
       <c r="D495">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="496">
@@ -9409,7 +9409,7 @@
         <v>6</v>
       </c>
       <c r="D503">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="504">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C509">
@@ -9733,7 +9733,7 @@
         <v>6</v>
       </c>
       <c r="D521">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="522">
@@ -10453,7 +10453,7 @@
         <v>6</v>
       </c>
       <c r="D561">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="562">
@@ -10489,7 +10489,7 @@
         <v>6</v>
       </c>
       <c r="D563">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="564">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C564">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C565">
@@ -10687,7 +10687,7 @@
         <v>6</v>
       </c>
       <c r="D574">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="575">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C582">
@@ -11713,7 +11713,7 @@
         <v>6</v>
       </c>
       <c r="D631">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="632">
@@ -12523,7 +12523,7 @@
         <v>6</v>
       </c>
       <c r="D676">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="677">
@@ -13279,7 +13279,7 @@
         <v>6</v>
       </c>
       <c r="D718">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="719">
@@ -13333,7 +13333,7 @@
         <v>6</v>
       </c>
       <c r="D721">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="722">
@@ -13549,7 +13549,7 @@
         <v>6</v>
       </c>
       <c r="D733">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="734">
@@ -13693,7 +13693,7 @@
         <v>6</v>
       </c>
       <c r="D741">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="742">
@@ -14179,7 +14179,7 @@
         <v>6</v>
       </c>
       <c r="D768">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="769">
@@ -14287,7 +14287,7 @@
         <v>6</v>
       </c>
       <c r="D774">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="775">
@@ -14539,7 +14539,7 @@
         <v>6</v>
       </c>
       <c r="D788">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="789">
@@ -14719,7 +14719,7 @@
         <v>6</v>
       </c>
       <c r="D798">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="799">
@@ -15061,7 +15061,7 @@
         <v>6</v>
       </c>
       <c r="D817">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="818">
@@ -15511,7 +15511,7 @@
         <v>6</v>
       </c>
       <c r="D842">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="843">
@@ -15547,7 +15547,7 @@
         <v>6</v>
       </c>
       <c r="D844">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="845">
@@ -15871,7 +15871,7 @@
         <v>6</v>
       </c>
       <c r="D862">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="863">
@@ -15943,7 +15943,7 @@
         <v>6</v>
       </c>
       <c r="D866">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="867">
@@ -16620,14 +16620,14 @@
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C904">
         <v>6</v>
       </c>
       <c r="D904">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="905">
@@ -16915,7 +16915,7 @@
         <v>6</v>
       </c>
       <c r="D920">
-        <v>0.000912270031929</v>
+        <v>0.0009122700319290002</v>
       </c>
     </row>
     <row r="921">
